--- a/Impact modelling/Correlations_energy_municipalities_months.xlsx
+++ b/Impact modelling/Correlations_energy_municipalities_months.xlsx
@@ -438,10 +438,10 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.5755252995906813</v>
+        <v>0.5689132190669172</v>
       </c>
       <c r="C2">
-        <v>13.16840950032727</v>
+        <v>13.16376063379492</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
@@ -453,10 +453,10 @@
         <v>11</v>
       </c>
       <c r="G2">
-        <v>0.7594438254139788</v>
+        <v>0.7554936949853113</v>
       </c>
       <c r="H2">
-        <v>7.080678049709893E-238</v>
+        <v>1.038597596659646E-180</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -464,10 +464,10 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>0.4265758941577582</v>
+        <v>0.5219333853117267</v>
       </c>
       <c r="C3">
-        <v>16.07823921683437</v>
+        <v>13.0900600765915</v>
       </c>
       <c r="D3" t="s">
         <v>7</v>
@@ -479,10 +479,10 @@
         <v>11</v>
       </c>
       <c r="G3">
-        <v>0.6567550823006009</v>
+        <v>0.7228219005786045</v>
       </c>
       <c r="H3">
-        <v>6.957550640652038E-136</v>
+        <v>2.959941936184043E-106</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -490,10 +490,10 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>0.555334328927336</v>
+        <v>0.5566629710062265</v>
       </c>
       <c r="C4">
-        <v>13.26250644364567</v>
+        <v>12.76353884383557</v>
       </c>
       <c r="D4" t="s">
         <v>7</v>
@@ -505,10 +505,10 @@
         <v>11</v>
       </c>
       <c r="G4">
-        <v>0.7490775323448819</v>
+        <v>0.7494005641123942</v>
       </c>
       <c r="H4">
-        <v>2.486704058620958E-149</v>
+        <v>1.494559325434353E-114</v>
       </c>
     </row>
   </sheetData>

--- a/Impact modelling/Correlations_energy_municipalities_months.xlsx
+++ b/Impact modelling/Correlations_energy_municipalities_months.xlsx
@@ -438,10 +438,10 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.5689132190669172</v>
+        <v>0.5182124975845352</v>
       </c>
       <c r="C2">
-        <v>13.16376063379492</v>
+        <v>13.33657455252095</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
@@ -453,10 +453,10 @@
         <v>11</v>
       </c>
       <c r="G2">
-        <v>0.7554936949853113</v>
+        <v>0.7252680494618466</v>
       </c>
       <c r="H2">
-        <v>1.038597596659646E-180</v>
+        <v>3.360745864948948E-199</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -464,10 +464,10 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>0.5219333853117267</v>
+        <v>0.3860864190236791</v>
       </c>
       <c r="C3">
-        <v>13.0900600765915</v>
+        <v>16.61233077506057</v>
       </c>
       <c r="D3" t="s">
         <v>7</v>
@@ -479,10 +479,10 @@
         <v>11</v>
       </c>
       <c r="G3">
-        <v>0.7228219005786045</v>
+        <v>0.6224747579306982</v>
       </c>
       <c r="H3">
-        <v>2.959941936184043E-106</v>
+        <v>9.597873181546618E-99</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -490,10 +490,10 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>0.5566629710062265</v>
+        <v>0.5011567141499469</v>
       </c>
       <c r="C4">
-        <v>12.76353884383557</v>
+        <v>12.59415370279113</v>
       </c>
       <c r="D4" t="s">
         <v>7</v>
@@ -505,10 +505,10 @@
         <v>11</v>
       </c>
       <c r="G4">
-        <v>0.7494005641123942</v>
+        <v>0.7155496672332626</v>
       </c>
       <c r="H4">
-        <v>1.494559325434353E-114</v>
+        <v>1.383930649300955E-146</v>
       </c>
     </row>
   </sheetData>
